--- a/Result/profitability/2352.xlsx
+++ b/Result/profitability/2352.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM80"/>
+  <dimension ref="A1:AM81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1975</v>
+        <v>0.1775</v>
       </c>
       <c r="N2" t="n">
-        <v>16.065</v>
+        <v>16.12875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.155</v>
+        <v>0.19</v>
       </c>
       <c r="N3" t="n">
-        <v>15.1675</v>
+        <v>15.28375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -893,10 +893,10 @@
         <v>-1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.10125</v>
+        <v>-0.08499999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>13.90125</v>
+        <v>13.89375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         <v>-0.98</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.255</v>
+        <v>-0.23</v>
       </c>
       <c r="N5" t="n">
-        <v>12.92625</v>
+        <v>13.0675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>-4.77</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.87375</v>
+        <v>-0.845</v>
       </c>
       <c r="N6" t="n">
-        <v>11.7175</v>
+        <v>11.765</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>-3.08</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2775</v>
+        <v>-1.23375</v>
       </c>
       <c r="N7" t="n">
-        <v>10.74625</v>
+        <v>10.7725</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1379,10 +1379,10 @@
         <v>1.14</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.13875</v>
+        <v>-1.11625</v>
       </c>
       <c r="N8" t="n">
-        <v>9.82</v>
+        <v>9.895</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1636,7 +1636,7 @@
         <v>-1.2675</v>
       </c>
       <c r="N10" t="n">
-        <v>8.122499999999999</v>
+        <v>8.1225</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2141,10 +2141,10 @@
         <v>0.44</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6850000000000002</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>8.684999999999999</v>
+        <v>8.685</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -2268,7 +2268,7 @@
         <v>-0.03</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3037500000000001</v>
+        <v>-0.30375</v>
       </c>
       <c r="N15" t="n">
         <v>9.1175</v>
@@ -2395,7 +2395,7 @@
         <v>0.9</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3337500000000002</v>
+        <v>-0.33375</v>
       </c>
       <c r="N16" t="n">
         <v>9.324999999999999</v>
@@ -2522,7 +2522,7 @@
         <v>0.47</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3150000000000001</v>
+        <v>-0.315</v>
       </c>
       <c r="N17" t="n">
         <v>10.13125</v>
@@ -2649,7 +2649,7 @@
         <v>0.23</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1587500000000001</v>
+        <v>-0.15875</v>
       </c>
       <c r="N18" t="n">
         <v>10.4375</v>
@@ -2776,7 +2776,7 @@
         <v>0.35</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1274999999999999</v>
+        <v>0.1275</v>
       </c>
       <c r="N19" t="n">
         <v>10.98875</v>
@@ -10576,6 +10576,133 @@
       </c>
       <c r="AM80" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>52730</v>
+      </c>
+      <c r="D81" t="n">
+        <v>43622</v>
+      </c>
+      <c r="E81" t="n">
+        <v>9108</v>
+      </c>
+      <c r="F81" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="G81" t="n">
+        <v>652</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>768</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1419</v>
+      </c>
+      <c r="K81" t="n">
+        <v>594</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.22875</v>
+      </c>
+      <c r="N81" t="n">
+        <v>16.8075</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
+      </c>
+      <c r="V81" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0.5999999999999979</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.03599280143971195</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>1.129999999999999</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0.07001239157372985</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK81" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
